--- a/schoolDocs/StudentImportData/Class3_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class3_ImportReady.xlsx
@@ -757,27 +757,27 @@
   <dimension ref="A1:U24"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="30.564" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="25.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="24.565" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="113.115" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" customWidth="true" style="0"/>
+    <col min="2" max="2" width="30.564" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.426" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.283" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.569" customWidth="true" style="0"/>
+    <col min="7" max="7" width="25.708" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.139" customWidth="true" style="0"/>
+    <col min="10" max="10" width="24.565" customWidth="true" style="0"/>
+    <col min="11" max="11" width="29.279" customWidth="true" style="0"/>
+    <col min="12" max="12" width="35.277" customWidth="true" style="0"/>
+    <col min="13" max="13" width="15.282" customWidth="true" style="0"/>
+    <col min="14" max="14" width="26.993" customWidth="true" style="0"/>
+    <col min="15" max="15" width="16.282" customWidth="true" style="0"/>
+    <col min="16" max="16" width="28.136" customWidth="true" style="0"/>
+    <col min="17" max="17" width="16.282" customWidth="true" style="0"/>
+    <col min="18" max="18" width="28.136" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
+    <col min="21" max="21" width="113.115" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -867,8 +867,10 @@
       <c r="H2" t="s">
         <v>25</v>
       </c>
+      <c r="I2"/>
+      <c r="J2"/>
       <c r="K2" s="5">
-        <v>6200</v>
+        <v>16200</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -908,6 +910,8 @@
       <c r="H3" t="s">
         <v>25</v>
       </c>
+      <c r="I3"/>
+      <c r="J3"/>
       <c r="K3">
         <v>16200</v>
       </c>
@@ -949,8 +953,10 @@
       <c r="H4" t="s">
         <v>25</v>
       </c>
+      <c r="I4"/>
+      <c r="J4"/>
       <c r="K4" s="5">
-        <v>9000</v>
+        <v>16200</v>
       </c>
       <c r="L4" t="s">
         <v>37</v>
@@ -990,6 +996,8 @@
       <c r="H5" t="s">
         <v>43</v>
       </c>
+      <c r="I5"/>
+      <c r="J5"/>
       <c r="K5">
         <v>16200</v>
       </c>
@@ -1025,8 +1033,10 @@
       <c r="H6" t="s">
         <v>43</v>
       </c>
+      <c r="I6"/>
+      <c r="J6"/>
       <c r="K6">
-        <v>12200</v>
+        <v>16200</v>
       </c>
       <c r="L6" t="s">
         <v>49</v>
@@ -1060,6 +1070,8 @@
       <c r="H7" t="s">
         <v>25</v>
       </c>
+      <c r="I7"/>
+      <c r="J7"/>
       <c r="K7">
         <v>16200</v>
       </c>
@@ -1101,6 +1113,11 @@
       <c r="H8" t="s">
         <v>57</v>
       </c>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8">
+        <v>0</v>
+      </c>
       <c r="L8" t="s">
         <v>58</v>
       </c>
@@ -1142,6 +1159,11 @@
       <c r="H9" t="s">
         <v>57</v>
       </c>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9">
+        <v>0</v>
+      </c>
       <c r="L9" t="s">
         <v>64</v>
       </c>
@@ -1171,6 +1193,11 @@
       <c r="H10" t="s">
         <v>57</v>
       </c>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10">
+        <v>0</v>
+      </c>
       <c r="L10" t="s">
         <v>67</v>
       </c>
@@ -1197,6 +1224,11 @@
       <c r="H11" t="s">
         <v>57</v>
       </c>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11">
+        <v>0</v>
+      </c>
       <c r="L11" t="s">
         <v>70</v>
       </c>
@@ -1229,6 +1261,8 @@
       <c r="H12" t="s">
         <v>43</v>
       </c>
+      <c r="I12"/>
+      <c r="J12"/>
       <c r="K12">
         <v>16200</v>
       </c>
@@ -1264,6 +1298,8 @@
       <c r="H13" t="s">
         <v>25</v>
       </c>
+      <c r="I13"/>
+      <c r="J13"/>
       <c r="K13">
         <v>12200</v>
       </c>
@@ -1305,8 +1341,9 @@
       <c r="I14">
         <v>25</v>
       </c>
+      <c r="J14"/>
       <c r="K14" s="5">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="L14" t="s">
         <v>81</v>
@@ -1352,6 +1389,10 @@
       <c r="I15">
         <v>25</v>
       </c>
+      <c r="J15"/>
+      <c r="K15">
+        <v>9150</v>
+      </c>
       <c r="L15" t="s">
         <v>87</v>
       </c>
@@ -1393,6 +1434,11 @@
       <c r="H16" t="s">
         <v>25</v>
       </c>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16">
+        <v>12200</v>
+      </c>
       <c r="L16" t="s">
         <v>91</v>
       </c>
@@ -1425,6 +1471,11 @@
       <c r="H17" t="s">
         <v>57</v>
       </c>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17">
+        <v>0</v>
+      </c>
       <c r="L17" t="s">
         <v>95</v>
       </c>
@@ -1466,6 +1517,8 @@
       <c r="H18" t="s">
         <v>25</v>
       </c>
+      <c r="I18"/>
+      <c r="J18"/>
       <c r="K18">
         <v>12200</v>
       </c>
@@ -1504,8 +1557,9 @@
       <c r="I19">
         <v>25</v>
       </c>
+      <c r="J19"/>
       <c r="K19">
-        <v>7000</v>
+        <v>9150</v>
       </c>
       <c r="L19" t="s">
         <v>101</v>
@@ -1542,8 +1596,10 @@
       <c r="H20" t="s">
         <v>25</v>
       </c>
+      <c r="I20"/>
+      <c r="J20"/>
       <c r="K20">
-        <v>6000</v>
+        <v>12200</v>
       </c>
       <c r="L20" t="s">
         <v>104</v>
@@ -1580,6 +1636,11 @@
       <c r="H21" t="s">
         <v>57</v>
       </c>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21">
+        <v>0</v>
+      </c>
       <c r="L21" t="s">
         <v>81</v>
       </c>
@@ -1609,6 +1670,11 @@
       <c r="H22" t="s">
         <v>57</v>
       </c>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22">
+        <v>0</v>
+      </c>
       <c r="L22" t="s">
         <v>58</v>
       </c>
@@ -1641,6 +1707,11 @@
       <c r="H23" t="s">
         <v>57</v>
       </c>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23">
+        <v>0</v>
+      </c>
       <c r="L23" t="s">
         <v>111</v>
       </c>
@@ -1672,6 +1743,11 @@
       </c>
       <c r="H24" t="s">
         <v>57</v>
+      </c>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24">
+        <v>0</v>
       </c>
       <c r="L24" t="s">
         <v>113</v>

--- a/schoolDocs/StudentImportData/Class3_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class3_ImportReady.xlsx
@@ -14,8 +14,34 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Calibri"/>
+            <b val="false"/>
+            <i val="false"/>
+            <strike val="false"/>
+            <color rgb="FF000000"/>
+            <sz val="11"/>
+            <u val="none"/>
+          </rPr>
+          <t xml:space="preserve">Only for RTE students. Alphanumeric, e.g. 26MS011157 (Year+StateCode+Sequence). Leave blank for non-RTE.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="112">
   <si>
     <t>Sr No</t>
   </si>
@@ -77,7 +103,7 @@
     <t>DGA Admission No</t>
   </si>
   <si>
-    <t>Notes for Verification (ignored on import)</t>
+    <t>RTE Application No</t>
   </si>
   <si>
     <t>Jaydeep Gaikwad</t>
@@ -110,9 +136,6 @@
     <t>Home maker</t>
   </si>
   <si>
-    <t>Partial — ₹6200 of ₹16200 collected</t>
-  </si>
-  <si>
     <t>Akshay Karde</t>
   </si>
   <si>
@@ -140,9 +163,6 @@
     <t>Sight Contractor</t>
   </si>
   <si>
-    <t>Partial — ₹9000 of ₹16200 collected</t>
-  </si>
-  <si>
     <t>Aman Ansari</t>
   </si>
   <si>
@@ -158,18 +178,12 @@
     <t>19km</t>
   </si>
   <si>
-    <t>CoC student — full ₹16200 collected</t>
-  </si>
-  <si>
     <t>Yash Lokhande</t>
   </si>
   <si>
     <t>12/01/2023</t>
   </si>
   <si>
-    <t>DGA shows ₹12200 for this CoC boy — system will use ₹16200. Please verify.</t>
-  </si>
-  <si>
     <t>Mark Dipak Tujare</t>
   </si>
   <si>
@@ -203,7 +217,7 @@
     <t>Brick Worker</t>
   </si>
   <si>
-    <t>RTE — fees paid by government</t>
+    <t>25MS000017</t>
   </si>
   <si>
     <t>Soham Motikar</t>
@@ -212,7 +226,7 @@
     <t>09/02/2021</t>
   </si>
   <si>
-    <t>RTE — G blank in DGA sheet</t>
+    <t>25MS000018</t>
   </si>
   <si>
     <t>Datta</t>
@@ -221,7 +235,7 @@
     <t>24/01/2023</t>
   </si>
   <si>
-    <t>Only first name — no surname. Please verify full name. RTE student.</t>
+    <t>25MS000019</t>
   </si>
   <si>
     <t>Ujer Firoj Pathan</t>
@@ -236,6 +250,9 @@
     <t>11km</t>
   </si>
   <si>
+    <t>25MS000020</t>
+  </si>
+  <si>
     <t>Sulatan Saror Shaikh</t>
   </si>
   <si>
@@ -272,9 +289,6 @@
     <t>Works at Bakery shop</t>
   </si>
   <si>
-    <t>Discount 25% on girls ₹12200 = ₹9150 payable — collected ₹3000 (partial)</t>
-  </si>
-  <si>
     <t>Vidya Lavaji Kokare</t>
   </si>
   <si>
@@ -284,9 +298,6 @@
     <t>Shepherd</t>
   </si>
   <si>
-    <t>Discount 25% on girls ₹12200 = ₹9150 payable — collected ₹0</t>
-  </si>
-  <si>
     <t>Bhakti Dilip Thote</t>
   </si>
   <si>
@@ -311,6 +322,9 @@
     <t>Supporting staff at DGA</t>
   </si>
   <si>
+    <t>25MS000021</t>
+  </si>
+  <si>
     <t>Srushti Dharmraj Athavale</t>
   </si>
   <si>
@@ -323,22 +337,16 @@
     <t>28/12/2020</t>
   </si>
   <si>
-    <t>DGA total ₹9150 but G col blank — assumed 25% discount. Collected ₹7000 partial. Please verify.</t>
-  </si>
-  <si>
     <t>Sannvi Manoj Musale</t>
   </si>
   <si>
     <t>02/12/2020</t>
   </si>
   <si>
-    <t>Partial — ₹6000 of ₹12200 collected</t>
-  </si>
-  <si>
     <t>Aaradhya Vinayak Shinde</t>
   </si>
   <si>
-    <t>RTE</t>
+    <t>25MS000022</t>
   </si>
   <si>
     <t>Mansi Somnath Thorat</t>
@@ -347,12 +355,18 @@
     <t>Varvand</t>
   </si>
   <si>
+    <t>25MS000023</t>
+  </si>
+  <si>
     <t>Shubhangi Bharat Jadhav</t>
   </si>
   <si>
     <t>13/12/2020</t>
   </si>
   <si>
+    <t>25MS000024</t>
+  </si>
+  <si>
     <t>Arya Gopal Dagde</t>
   </si>
   <si>
@@ -360,6 +374,9 @@
   </si>
   <si>
     <t>Tulevasti</t>
+  </si>
+  <si>
+    <t>25MS000025</t>
   </si>
 </sst>
 </file>
@@ -411,12 +428,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7B3F00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -424,6 +435,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5EAD0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -445,16 +462,16 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -777,7 +794,7 @@
     <col min="18" max="18" width="28.136" customWidth="true" style="0"/>
     <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
     <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
-    <col min="21" max="21" width="113.115" customWidth="true" style="0"/>
+    <col min="21" max="21" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -811,10 +828,10 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -841,7 +858,7 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -869,7 +886,7 @@
       </c>
       <c r="I2"/>
       <c r="J2"/>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <v>16200</v>
       </c>
       <c r="L2" t="s">
@@ -887,16 +904,14 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
-      <c r="U2" t="s">
-        <v>31</v>
-      </c>
+      <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -916,7 +931,7 @@
         <v>16200</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
         <v>27</v>
@@ -925,18 +940,19 @@
         <v>28</v>
       </c>
       <c r="P3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" t="s">
         <v>34</v>
       </c>
-      <c r="R3" t="s">
-        <v>35</v>
-      </c>
+      <c r="U3"/>
     </row>
     <row r="4" spans="1:21">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -955,34 +971,32 @@
       </c>
       <c r="I4"/>
       <c r="J4"/>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>16200</v>
       </c>
       <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
         <v>37</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>38</v>
       </c>
-      <c r="N4" t="s">
+      <c r="P4" t="s">
         <v>39</v>
-      </c>
-      <c r="P4" t="s">
-        <v>40</v>
       </c>
       <c r="R4" t="s">
         <v>30</v>
       </c>
-      <c r="U4" t="s">
-        <v>41</v>
-      </c>
+      <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -994,7 +1008,7 @@
         <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -1002,24 +1016,22 @@
         <v>16200</v>
       </c>
       <c r="L5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
         <v>44</v>
       </c>
-      <c r="M5" t="s">
-        <v>45</v>
-      </c>
-      <c r="N5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U5" t="s">
-        <v>47</v>
-      </c>
+      <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1031,7 +1043,7 @@
         <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -1039,24 +1051,22 @@
         <v>16200</v>
       </c>
       <c r="L6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>50</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="U6" s="4"/>
     </row>
     <row r="7" spans="1:21">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -1076,27 +1086,28 @@
         <v>16200</v>
       </c>
       <c r="L7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="P7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="R7" t="s">
         <v>30</v>
       </c>
+      <c r="U7"/>
     </row>
     <row r="8" spans="1:21">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -1111,7 +1122,7 @@
         <v>7020692613</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -1119,22 +1130,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="N8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="P8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R8" t="s">
         <v>30</v>
       </c>
       <c r="U8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1142,7 +1153,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -1157,7 +1168,7 @@
         <v>9890986259</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1165,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="U9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1176,7 +1187,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -1191,7 +1202,7 @@
         <v>9699873105</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1199,10 +1210,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>67</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1210,7 +1221,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
@@ -1222,7 +1233,7 @@
         <v>24</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1230,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="U11" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -1247,7 +1258,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
@@ -1259,7 +1270,7 @@
         <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1267,27 +1278,25 @@
         <v>16200</v>
       </c>
       <c r="L12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N12" t="s">
-        <v>46</v>
-      </c>
-      <c r="U12" t="s">
-        <v>47</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="U12"/>
     </row>
     <row r="13" spans="1:21">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -1304,7 +1313,7 @@
         <v>12200</v>
       </c>
       <c r="L13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M13" t="s">
         <v>27</v>
@@ -1313,21 +1322,22 @@
         <v>28</v>
       </c>
       <c r="P13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R13" t="s">
-        <v>78</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="U13"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -1336,43 +1346,41 @@
         <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I14">
         <v>25</v>
       </c>
       <c r="J14"/>
-      <c r="K14" s="5">
+      <c r="K14" s="4">
         <v>5000</v>
       </c>
       <c r="L14" t="s">
+        <v>78</v>
+      </c>
+      <c r="M14" t="s">
+        <v>79</v>
+      </c>
+      <c r="N14" t="s">
+        <v>80</v>
+      </c>
+      <c r="P14" t="s">
         <v>81</v>
-      </c>
-      <c r="M14" t="s">
-        <v>82</v>
-      </c>
-      <c r="N14" t="s">
-        <v>83</v>
-      </c>
-      <c r="P14" t="s">
-        <v>84</v>
       </c>
       <c r="R14" t="s">
         <v>30</v>
       </c>
-      <c r="U14" t="s">
-        <v>85</v>
-      </c>
+      <c r="U14"/>
     </row>
     <row r="15" spans="1:21">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -1384,7 +1392,7 @@
         <v>9975332700</v>
       </c>
       <c r="H15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I15">
         <v>25</v>
@@ -1394,33 +1402,31 @@
         <v>9150</v>
       </c>
       <c r="L15" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N15" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="R15" t="s">
         <v>30</v>
       </c>
-      <c r="U15" t="s">
-        <v>89</v>
-      </c>
+      <c r="U15"/>
     </row>
     <row r="16" spans="1:21">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -1440,24 +1446,25 @@
         <v>12200</v>
       </c>
       <c r="L16" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="N16" t="s">
-        <v>93</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="U16"/>
     </row>
     <row r="17" spans="1:21">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>23</v>
@@ -1469,7 +1476,7 @@
         <v>7057125914</v>
       </c>
       <c r="H17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -1477,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M17" t="s">
         <v>27</v>
@@ -1486,13 +1493,13 @@
         <v>28</v>
       </c>
       <c r="P17" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="R17" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="U17" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -1500,10 +1507,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
@@ -1523,24 +1530,25 @@
         <v>12200</v>
       </c>
       <c r="L18" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M18" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="N18" t="s">
-        <v>93</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="U18"/>
     </row>
     <row r="19" spans="1:21">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
         <v>23</v>
@@ -1552,7 +1560,7 @@
         <v>9579020523</v>
       </c>
       <c r="H19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I19">
         <v>25</v>
@@ -1562,7 +1570,7 @@
         <v>9150</v>
       </c>
       <c r="L19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="M19" t="s">
         <v>27</v>
@@ -1570,19 +1578,17 @@
       <c r="N19" t="s">
         <v>28</v>
       </c>
-      <c r="U19" s="5" t="s">
-        <v>102</v>
-      </c>
+      <c r="U19" s="4"/>
     </row>
     <row r="20" spans="1:21">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s">
         <v>23</v>
@@ -1602,27 +1608,25 @@
         <v>12200</v>
       </c>
       <c r="L20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="M20" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="N20" t="s">
-        <v>93</v>
-      </c>
-      <c r="U20" t="s">
-        <v>105</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="U20"/>
     </row>
     <row r="21" spans="1:21">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
         <v>23</v>
@@ -1634,7 +1638,7 @@
         <v>9922809600</v>
       </c>
       <c r="H21" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -1642,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="U21" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -1653,10 +1657,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
         <v>23</v>
@@ -1668,7 +1672,7 @@
         <v>8007924257</v>
       </c>
       <c r="H22" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -1676,16 +1680,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M22" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="N22" t="s">
         <v>28</v>
       </c>
       <c r="U22" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -1693,10 +1697,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
         <v>23</v>
@@ -1705,7 +1709,7 @@
         <v>24</v>
       </c>
       <c r="H23" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -1713,16 +1717,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="M23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="U23" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -1730,10 +1734,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
         <v>23</v>
@@ -1742,7 +1746,7 @@
         <v>24</v>
       </c>
       <c r="H24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -1750,16 +1754,16 @@
         <v>0</v>
       </c>
       <c r="L24" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="M24" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="U24" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1774,6 +1778,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId_comments_vml1"/>
   <tableParts count="0"/>
 </worksheet>
 </file>
--- a/schoolDocs/StudentImportData/Class3_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class3_ImportReady.xlsx
@@ -904,6 +904,9 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
+      <c r="S2">
+        <v>27000010036</v>
+      </c>
       <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
@@ -945,6 +948,9 @@
       <c r="R3" t="s">
         <v>34</v>
       </c>
+      <c r="S3">
+        <v>27000010037</v>
+      </c>
       <c r="U3"/>
     </row>
     <row r="4" spans="1:21">
@@ -989,6 +995,9 @@
       <c r="R4" t="s">
         <v>30</v>
       </c>
+      <c r="S4">
+        <v>27000010038</v>
+      </c>
       <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
@@ -1024,6 +1033,9 @@
       <c r="N5" t="s">
         <v>44</v>
       </c>
+      <c r="S5">
+        <v>27000010039</v>
+      </c>
       <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
@@ -1059,6 +1071,9 @@
       <c r="N6" t="s">
         <v>44</v>
       </c>
+      <c r="S6">
+        <v>27000010040</v>
+      </c>
       <c r="U6" s="4"/>
     </row>
     <row r="7" spans="1:21">
@@ -1100,6 +1115,9 @@
       <c r="R7" t="s">
         <v>30</v>
       </c>
+      <c r="S7">
+        <v>27000010041</v>
+      </c>
       <c r="U7"/>
     </row>
     <row r="8" spans="1:21">
@@ -1144,6 +1162,9 @@
       <c r="R8" t="s">
         <v>30</v>
       </c>
+      <c r="S8">
+        <v>27000010042</v>
+      </c>
       <c r="U8" t="s">
         <v>58</v>
       </c>
@@ -1178,6 +1199,9 @@
       <c r="L9" t="s">
         <v>60</v>
       </c>
+      <c r="S9">
+        <v>27000010043</v>
+      </c>
       <c r="U9" t="s">
         <v>61</v>
       </c>
@@ -1212,6 +1236,9 @@
       <c r="L10" t="s">
         <v>63</v>
       </c>
+      <c r="S10">
+        <v>27000010044</v>
+      </c>
       <c r="U10" s="4" t="s">
         <v>64</v>
       </c>
@@ -1249,6 +1276,9 @@
       <c r="N11" t="s">
         <v>68</v>
       </c>
+      <c r="S11">
+        <v>27000010045</v>
+      </c>
       <c r="U11" t="s">
         <v>69</v>
       </c>
@@ -1286,6 +1316,9 @@
       <c r="N12" t="s">
         <v>44</v>
       </c>
+      <c r="S12">
+        <v>27000010046</v>
+      </c>
       <c r="U12"/>
     </row>
     <row r="13" spans="1:21">
@@ -1327,6 +1360,9 @@
       <c r="R13" t="s">
         <v>75</v>
       </c>
+      <c r="S13">
+        <v>27000010047</v>
+      </c>
       <c r="U13"/>
     </row>
     <row r="14" spans="1:21">
@@ -1370,6 +1406,9 @@
       <c r="R14" t="s">
         <v>30</v>
       </c>
+      <c r="S14">
+        <v>27000010048</v>
+      </c>
       <c r="U14"/>
     </row>
     <row r="15" spans="1:21">
@@ -1415,6 +1454,9 @@
       </c>
       <c r="R15" t="s">
         <v>30</v>
+      </c>
+      <c r="S15">
+        <v>27000010049</v>
       </c>
       <c r="U15"/>
     </row>
@@ -1454,6 +1496,9 @@
       <c r="N16" t="s">
         <v>88</v>
       </c>
+      <c r="S16">
+        <v>27000010050</v>
+      </c>
       <c r="U16"/>
     </row>
     <row r="17" spans="1:21">
@@ -1498,6 +1543,9 @@
       <c r="R17" t="s">
         <v>92</v>
       </c>
+      <c r="S17">
+        <v>27000010051</v>
+      </c>
       <c r="U17" t="s">
         <v>93</v>
       </c>
@@ -1538,6 +1586,9 @@
       <c r="N18" t="s">
         <v>88</v>
       </c>
+      <c r="S18">
+        <v>27000010052</v>
+      </c>
       <c r="U18"/>
     </row>
     <row r="19" spans="1:21">
@@ -1577,6 +1628,9 @@
       </c>
       <c r="N19" t="s">
         <v>28</v>
+      </c>
+      <c r="S19">
+        <v>27000010053</v>
       </c>
       <c r="U19" s="4"/>
     </row>
@@ -1616,6 +1670,9 @@
       <c r="N20" t="s">
         <v>88</v>
       </c>
+      <c r="S20">
+        <v>27000010054</v>
+      </c>
       <c r="U20"/>
     </row>
     <row r="21" spans="1:21">
@@ -1648,6 +1705,9 @@
       <c r="L21" t="s">
         <v>78</v>
       </c>
+      <c r="S21">
+        <v>27000010055</v>
+      </c>
       <c r="U21" t="s">
         <v>101</v>
       </c>
@@ -1688,6 +1748,9 @@
       <c r="N22" t="s">
         <v>28</v>
       </c>
+      <c r="S22">
+        <v>27000010056</v>
+      </c>
       <c r="U22" t="s">
         <v>104</v>
       </c>
@@ -1725,6 +1788,9 @@
       <c r="N23" t="s">
         <v>80</v>
       </c>
+      <c r="S23">
+        <v>27000010057</v>
+      </c>
       <c r="U23" t="s">
         <v>107</v>
       </c>
@@ -1761,6 +1827,9 @@
       </c>
       <c r="N24" t="s">
         <v>56</v>
+      </c>
+      <c r="S24">
+        <v>27000010058</v>
       </c>
       <c r="U24" t="s">
         <v>111</v>
